--- a/StructureDefinition-mii-pr-fall-kontakt-gesundheitseinrichtung.xlsx
+++ b/StructureDefinition-mii-pr-fall-kontakt-gesundheitseinrichtung.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.0.1</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15</t>
+    <t>2026-09-01</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5611,7 +5611,7 @@
         <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>80</v>
+        <v>192</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>115</v>
@@ -5722,7 +5722,7 @@
         <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>80</v>
+        <v>192</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>115</v>
@@ -5942,7 +5942,7 @@
         <v>79</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>80</v>
+        <v>192</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>115</v>
@@ -6160,7 +6160,7 @@
         <v>87</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>80</v>
+        <v>192</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>99</v>
@@ -6271,7 +6271,7 @@
         <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>80</v>
+        <v>192</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>115</v>
@@ -6491,7 +6491,7 @@
         <v>79</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>80</v>
+        <v>192</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>115</v>
@@ -6709,7 +6709,7 @@
         <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>80</v>
+        <v>192</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>99</v>
@@ -6820,7 +6820,7 @@
         <v>79</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>80</v>
+        <v>192</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>115</v>
@@ -7040,7 +7040,7 @@
         <v>79</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>80</v>
+        <v>192</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>115</v>
@@ -7258,7 +7258,7 @@
         <v>87</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>80</v>
+        <v>192</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>99</v>
@@ -7478,7 +7478,7 @@
         <v>87</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>80</v>
+        <v>192</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>99</v>
@@ -28433,7 +28433,7 @@
         <v>79</v>
       </c>
       <c r="AI226" t="s" s="2">
-        <v>80</v>
+        <v>192</v>
       </c>
       <c r="AJ226" t="s" s="2">
         <v>115</v>
@@ -28544,7 +28544,7 @@
         <v>79</v>
       </c>
       <c r="AI227" t="s" s="2">
-        <v>80</v>
+        <v>192</v>
       </c>
       <c r="AJ227" t="s" s="2">
         <v>115</v>
@@ -28764,7 +28764,7 @@
         <v>79</v>
       </c>
       <c r="AI229" t="s" s="2">
-        <v>80</v>
+        <v>192</v>
       </c>
       <c r="AJ229" t="s" s="2">
         <v>115</v>
@@ -28982,7 +28982,7 @@
         <v>87</v>
       </c>
       <c r="AI231" t="s" s="2">
-        <v>80</v>
+        <v>192</v>
       </c>
       <c r="AJ231" t="s" s="2">
         <v>99</v>
@@ -29093,7 +29093,7 @@
         <v>79</v>
       </c>
       <c r="AI232" t="s" s="2">
-        <v>80</v>
+        <v>192</v>
       </c>
       <c r="AJ232" t="s" s="2">
         <v>115</v>
@@ -29313,7 +29313,7 @@
         <v>79</v>
       </c>
       <c r="AI234" t="s" s="2">
-        <v>80</v>
+        <v>192</v>
       </c>
       <c r="AJ234" t="s" s="2">
         <v>115</v>
@@ -29531,7 +29531,7 @@
         <v>87</v>
       </c>
       <c r="AI236" t="s" s="2">
-        <v>80</v>
+        <v>192</v>
       </c>
       <c r="AJ236" t="s" s="2">
         <v>99</v>
@@ -29751,7 +29751,7 @@
         <v>87</v>
       </c>
       <c r="AI238" t="s" s="2">
-        <v>80</v>
+        <v>192</v>
       </c>
       <c r="AJ238" t="s" s="2">
         <v>99</v>

--- a/StructureDefinition-mii-pr-fall-kontakt-gesundheitseinrichtung.xlsx
+++ b/StructureDefinition-mii-pr-fall-kontakt-gesundheitseinrichtung.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
